--- a/stories/arbres/TREE-SAN-003.xlsx
+++ b/stories/arbres/TREE-SAN-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya joue au parc avec maman. Papa arrive aussi. Le soleil tape. Maya a soif. Sa bouche est sèche. Maman a un verre. Dedans, il y a de l'eau. Quand on a soif, on boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1517,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1519,7 +1546,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya creuse au bac à sable. Le sable est chaud. Elle a soif. Maman tend un verre. Maya boit de l'eau dans le verre. L'eau est fraîche. Papa dit : quand on a soif, on boit de l'eau.</t>
+          <t>Maya creuse au bac à sable. Le sable est chaud. Elle a soif. Maman tend un verre. Maya boit de l'eau dans le verre. L'eau est fraîche. Quand on a soif, on boit de l'eau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1657,6 +1684,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya creuse au bac à sable. Le sable est chaud. Elle a soif. Maman tend un verre. Maya boit de l'eau dans le verre. L'eau est fraîche.
+papa|Quand on a soif, on boit de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1870,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a soif. Que boit-elle ?</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2043,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a bu. L'eau était dans le verre. La soif est partie. Elle peut rejouer.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2199,6 +2242,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2223,7 +2271,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom a le sable aux mains. Il a soif aussi. Maman verse de l'eau dans un verre. Tom boit. Maya dit : l'eau, dans le verre. Quand on a soif.</t>
+          <t>Tom a le sable aux mains. Il a soif aussi. Maman verse de l'eau dans un verre. Tom boit. L'eau, dans le verre. Quand on a soif.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2361,6 +2409,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a le sable aux mains. Il a soif aussi. Maman verse de l'eau dans un verre. Tom boit.
+enfant-f|L'eau, dans le verre. Quand on a soif.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2551,6 +2605,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2772,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, le parc est calme. Maya a soif. Elle boit de l'eau dans un verre. Tom aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2939,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2899,7 +2968,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Maya a soif. Elle prend le verre. Elle boit de l'eau. Tom dit : encore un peu.</t>
+          <t>Après la sieste, Maya a soif. Elle prend le verre. Elle boit de l'eau. Encore un peu.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3037,6 +3106,12 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Maya a soif. Elle prend le verre. Elle boit de l'eau.
+enfant-m|Encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3199,6 +3274,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3361,6 +3441,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, l'air est plus doux. Maya a soif. Elle boit de l'eau dans un verre. Tom range le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3523,6 +3608,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3685,6 +3775,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit au bord du bac. Elle a soif. Papa donne un verre d'eau. Léa boit. Maya boit aussi. L'eau coule, fraîche.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3875,6 +3970,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4037,6 +4137,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa a soif. Maya lui passe le verre. Elles boivent de l'eau. La soif s'en va.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4199,6 +4304,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4361,6 +4471,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Léa bâille. Elle a soif. Maya boit de l'eau dans un verre. Léa aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4523,6 +4638,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4685,6 +4805,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Léa a encore soif. Maya prend le verre. Elles boivent de l'eau. Maman range.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4847,6 +4972,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4871,7 +5001,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami a bâti un château. Il a soif. Maya lui montre le verre. Sami boit de l'eau. Maya dit : j'avais soif. L'eau m'a aidée.</t>
+          <t>Sami a bâti un château. Il a soif. Maya lui montre le verre. Sami boit de l'eau. J'avais soif. L'eau m'a aidée.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5009,6 +5139,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a bâti un château. Il a soif. Maya lui montre le verre. Sami boit de l'eau.
+enfant-f|J'avais soif. L'eau m'a aidée.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5199,6 +5335,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5361,6 +5502,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami a soif. Maya boit de l'eau dans un verre. Sami aussi. Le château reste.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5523,6 +5669,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5685,6 +5836,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Sami a chaud. Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5847,6 +6003,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5871,7 +6032,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Sami range. Maya a soif. Elle boit de l'eau dans un verre. Papa dit : bien.</t>
+          <t>Le soir, Sami range. Maya a soif. Elle boit de l'eau dans un verre. Bien.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6009,6 +6170,12 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Sami range. Maya a soif. Elle boit de l'eau dans un verre.
+papa|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6171,6 +6338,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6195,7 +6367,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Maya gravit le petit toboggan. En haut, elle a soif. Elle redescend. Maman l'attend avec un verre. Maya boit de l'eau. L'eau glisse, fraîche. Papa dit : soif, alors un verre d'eau.</t>
+          <t>Maya gravit le petit toboggan. En haut, elle a soif. Elle redescend. Maman l'attend avec un verre. Maya boit de l'eau. L'eau glisse, fraîche. Soif, alors un verre d'eau.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6333,6 +6505,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya gravit le petit toboggan. En haut, elle a soif. Elle redescend. Maman l'attend avec un verre. Maya boit de l'eau. L'eau glisse, fraîche.
+papa|Soif, alors un verre d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6509,6 +6687,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Maya redescend. Que boit-elle ?</t>
         </is>
       </c>
     </row>
@@ -6677,6 +6860,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Après le toboggan, Maya a bu. L'eau était dans le verre. La soif est partie.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6871,6 +7059,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6895,7 +7088,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tom glisse aussi. Il a soif. Maman remplit le verre d'eau. Tom boit. Maya dit : quand on a soif, un verre d'eau.</t>
+          <t>Tom glisse aussi. Il a soif. Maman remplit le verre d'eau. Tom boit. Quand on a soif, un verre d'eau.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7033,6 +7226,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom glisse aussi. Il a soif. Maman remplit le verre d'eau. Tom boit.
+enfant-f|Quand on a soif, un verre d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7223,6 +7422,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7385,6 +7589,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, le toboggan est frais. Maya a soif. Elle boit de l'eau dans un verre. Tom aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7547,6 +7756,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7709,6 +7923,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Tom a chaud. Maya boit de l'eau dans un verre. La soif s'en va.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7871,6 +8090,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8033,6 +8257,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, ils glissent une dernière fois. Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8195,6 +8424,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8357,6 +8591,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa attend en bas. Elle a soif. Papa tend le verre d'eau. Léa boit. Maya boit. Elles soufflent. Plus soif.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8547,6 +8786,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8709,6 +8953,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa a soif. Maya lui donne le verre. Elles boivent de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8871,6 +9120,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9033,6 +9287,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Léa a les joues chaudes. Maya boit de l'eau dans un verre. Léa aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9195,6 +9454,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9219,7 +9483,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Léa dit : encore un peu. Maya a soif. Elle boit de l'eau dans un verre.</t>
+          <t>Le soir, Encore un peu. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9357,6 +9621,13 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir,
+enfant-f|Encore un peu.
+narrateur|Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9519,6 +9790,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9543,7 +9819,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sami tient les montants. Il a soif. Maya passe le verre. Sami boit de l'eau. Maya dit : l'eau, c'est pour la soif.</t>
+          <t>Sami tient les montants. Il a soif. Maya passe le verre. Sami boit de l'eau. L'eau, c'est pour la soif.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9681,6 +9957,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami tient les montants. Il a soif. Maya passe le verre. Sami boit de l'eau.
+enfant-f|L'eau, c'est pour la soif.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9871,6 +10153,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10033,6 +10320,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami a soif. Maya boit de l'eau dans un verre. Ils se tapent dans les mains.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10195,6 +10487,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10357,6 +10654,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Sami a la bouche sèche. Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10519,6 +10821,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10681,6 +10988,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Sami range ses chaussures. Maya boit de l'eau dans un verre. La soif est partie.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10843,6 +11155,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10867,7 +11184,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya se balance. L'air bouge. Elle a soif. Elle s'arrête. Maman est là, avec un verre d'eau. Maya boit. L'eau est froide. Papa dit : bien. Quand on a soif, on boit de l'eau dans un verre.</t>
+          <t>Maya se balance. L'air bouge. Elle a soif. Elle s'arrête. Maman est là, avec un verre d'eau. Maya boit. L'eau est froide. Bien. Quand on a soif, on boit de l'eau dans un verre.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11005,6 +11322,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya se balance. L'air bouge. Elle a soif. Elle s'arrête. Maman est là, avec un verre d'eau. Maya boit. L'eau est froide.
+papa|Bien. Quand on a soif, on boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11181,6 +11504,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Maya s'arrête. Que boit-elle ?</t>
         </is>
       </c>
     </row>
@@ -11349,6 +11677,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a bu à la balançoire. L'eau dans le verre a calmé la soif.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11543,6 +11876,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11567,7 +11905,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tom se balance tout doux. Il a soif. Maman verse de l'eau dans le verre. Tom boit. Maya dit : j'avais soif. L'eau, c'est bien.</t>
+          <t>Tom se balance tout doux. Il a soif. Maman verse de l'eau dans le verre. Tom boit. J'avais soif. L'eau, c'est bien.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11705,6 +12043,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se balance tout doux. Il a soif. Maman verse de l'eau dans le verre. Tom boit.
+enfant-f|J'avais soif. L'eau, c'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11895,6 +12239,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12057,6 +12406,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, la balançoire craque. Maya a soif. Elle boit de l'eau dans un verre. Tom aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12219,6 +12573,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12381,6 +12740,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Tom a soif. Maya boit de l'eau dans un verre. Ils se reposent.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12543,6 +12907,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12567,7 +12936,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Tom dit : encore. Maya a soif. Elle boit de l'eau dans un verre.</t>
+          <t>Le soir, Encore. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12705,6 +13074,13 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir,
+enfant-m|Encore.
+narrateur|Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12867,6 +13243,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13029,6 +13410,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se balance en face. Elle a soif. Papa donne le verre d'eau. Léa boit. Maya boit. Elles sourient. Plus de soif.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13219,6 +13605,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13381,6 +13772,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa a soif. Maya prend le verre. Elles boivent de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13543,6 +13939,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13705,6 +14106,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Léa a chaud. Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13867,6 +14273,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14029,6 +14440,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Léa range son manteau. Maya boit de l'eau dans un verre. La soif s'en va.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14191,6 +14607,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14215,7 +14636,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami pousse tout doux. Il a soif. Maya lui offre le verre. Sami boit de l'eau. Maya dit : soif, alors de l'eau.</t>
+          <t>Sami pousse tout doux. Il a soif. Maya lui offre le verre. Sami boit de l'eau. Soif, alors de l'eau.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14353,6 +14774,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pousse tout doux. Il a soif. Maya lui offre le verre. Sami boit de l'eau.
+enfant-f|Soif, alors de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14543,6 +14970,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14705,6 +15137,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami a soif. Maya boit de l'eau dans un verre. Sami aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14867,6 +15304,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15029,6 +15471,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Sami a les lèvres sèches. Maya a soif. Elle boit de l'eau dans un verre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15191,6 +15638,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15353,6 +15805,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Sami dit merci. Maya a soif. Elle boit de l'eau dans un verre. Papa range le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15515,6 +15972,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15533,7 +15995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15571,6 +16033,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-003.xlsx
+++ b/stories/arbres/TREE-SAN-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Maya joue au parc avec maman. Papa arrive aussi. Le soleil tape. Maya a soif. Sa bouche est sèche. Maman a un verre. Dedans, il y a de l'eau. Quand on a soif, on boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1522,6 +1532,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1690,6 +1701,7 @@
 papa|Quand on a soif, on boit de l'eau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1877,6 +1889,7 @@
           <t>narrateur|Maya a soif. Que boit-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2048,6 +2061,7 @@
           <t>narrateur|Maya a bu. L'eau était dans le verre. La soif est partie. Elle peut rejouer.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2247,6 +2261,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2415,6 +2430,7 @@
 enfant-f|L'eau, dans le verre. Quand on a soif.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2610,6 +2626,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2777,6 +2794,11 @@
           <t>narrateur|Le matin, le parc est calme. Maya a soif. Elle boit de l'eau dans un verre. Tom aussi.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2944,6 +2966,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3112,6 +3135,7 @@
 enfant-m|Encore un peu.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3279,6 +3303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3446,6 +3471,7 @@
           <t>narrateur|Le soir, l'air est plus doux. Maya a soif. Elle boit de l'eau dans un verre. Tom range le seau.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3613,6 +3639,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3780,6 +3807,7 @@
           <t>narrateur|Léa s'assoit au bord du bac. Elle a soif. Papa donne un verre d'eau. Léa boit. Maya boit aussi. L'eau coule, fraîche.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3975,6 +4003,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4142,6 +4171,7 @@
           <t>narrateur|Le matin, Léa a soif. Maya lui passe le verre. Elles boivent de l'eau. La soif s'en va.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4309,6 +4339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4476,6 +4507,7 @@
           <t>narrateur|Après la sieste, Léa bâille. Elle a soif. Maya boit de l'eau dans un verre. Léa aussi.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4643,6 +4675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4810,6 +4843,7 @@
           <t>narrateur|Le soir, Léa a encore soif. Maya prend le verre. Elles boivent de l'eau. Maman range.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4977,6 +5011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5145,6 +5180,7 @@
 enfant-f|J'avais soif. L'eau m'a aidée.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5340,6 +5376,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5507,6 +5544,7 @@
           <t>narrateur|Le matin, Sami a soif. Maya boit de l'eau dans un verre. Sami aussi. Le château reste.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5674,6 +5712,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5841,6 +5880,7 @@
           <t>narrateur|Après la sieste, Sami a chaud. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6008,6 +6048,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6176,6 +6217,7 @@
 papa|Bien.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6343,6 +6385,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6511,6 +6554,7 @@
 papa|Soif, alors un verre d'eau.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6694,6 +6738,7 @@
           <t>narrateur|Maya redescend. Que boit-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6865,6 +6910,7 @@
           <t>narrateur|Après le toboggan, Maya a bu. L'eau était dans le verre. La soif est partie.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7064,6 +7110,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7232,6 +7279,7 @@
 enfant-f|Quand on a soif, un verre d'eau.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7427,6 +7475,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7594,6 +7643,7 @@
           <t>narrateur|Le matin, le toboggan est frais. Maya a soif. Elle boit de l'eau dans un verre. Tom aussi.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7761,6 +7811,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7928,6 +7979,7 @@
           <t>narrateur|Après la sieste, Tom a chaud. Maya boit de l'eau dans un verre. La soif s'en va.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8095,6 +8147,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8262,6 +8315,7 @@
           <t>narrateur|Le soir, ils glissent une dernière fois. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8429,6 +8483,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8596,6 +8651,7 @@
           <t>narrateur|Léa attend en bas. Elle a soif. Papa tend le verre d'eau. Léa boit. Maya boit. Elles soufflent. Plus soif.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8791,6 +8847,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8958,6 +9015,7 @@
           <t>narrateur|Le matin, Léa a soif. Maya lui donne le verre. Elles boivent de l'eau.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9125,6 +9183,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9292,6 +9351,7 @@
           <t>narrateur|Après la sieste, Léa a les joues chaudes. Maya boit de l'eau dans un verre. Léa aussi.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9459,6 +9519,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9628,6 +9689,7 @@
 narrateur|Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9795,6 +9857,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9963,6 +10026,7 @@
 enfant-f|L'eau, c'est pour la soif.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10158,6 +10222,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10325,6 +10390,7 @@
           <t>narrateur|Le matin, Sami a soif. Maya boit de l'eau dans un verre. Ils se tapent dans les mains.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10492,6 +10558,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10659,6 +10726,7 @@
           <t>narrateur|Après la sieste, Sami a la bouche sèche. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10826,6 +10894,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10993,6 +11062,7 @@
           <t>narrateur|Le soir, Sami range ses chaussures. Maya boit de l'eau dans un verre. La soif est partie.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11160,6 +11230,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11328,6 +11399,7 @@
 papa|Bien. Quand on a soif, on boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11511,6 +11583,7 @@
           <t>narrateur|Maya s'arrête. Que boit-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11682,6 +11755,7 @@
           <t>narrateur|Maya a bu à la balançoire. L'eau dans le verre a calmé la soif.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11881,6 +11955,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12049,6 +12124,7 @@
 enfant-f|J'avais soif. L'eau, c'est bien.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12244,6 +12320,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12411,6 +12488,7 @@
           <t>narrateur|Le matin, la balançoire craque. Maya a soif. Elle boit de l'eau dans un verre. Tom aussi.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12578,6 +12656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12745,6 +12824,7 @@
           <t>narrateur|Après la sieste, Tom a soif. Maya boit de l'eau dans un verre. Ils se reposent.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12912,6 +12992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13081,6 +13162,7 @@
 narrateur|Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13248,6 +13330,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13415,6 +13498,7 @@
           <t>narrateur|Léa se balance en face. Elle a soif. Papa donne le verre d'eau. Léa boit. Maya boit. Elles sourient. Plus de soif.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13610,6 +13694,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13777,6 +13862,7 @@
           <t>narrateur|Le matin, Léa a soif. Maya prend le verre. Elles boivent de l'eau.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13944,6 +14030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14111,6 +14198,7 @@
           <t>narrateur|Après la sieste, Léa a chaud. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14278,6 +14366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14445,6 +14534,7 @@
           <t>narrateur|Le soir, Léa range son manteau. Maya boit de l'eau dans un verre. La soif s'en va.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14612,6 +14702,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14780,6 +14871,7 @@
 enfant-f|Soif, alors de l'eau.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14975,6 +15067,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15142,6 +15235,7 @@
           <t>narrateur|Le matin, Sami a soif. Maya boit de l'eau dans un verre. Sami aussi.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15309,6 +15403,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15476,6 +15571,7 @@
           <t>narrateur|Après la sieste, Sami a les lèvres sèches. Maya a soif. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15643,6 +15739,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15810,6 +15907,7 @@
           <t>narrateur|Le soir, Sami dit merci. Maya a soif. Elle boit de l'eau dans un verre. Papa range le verre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15977,6 +16075,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15995,7 +16094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16040,6 +16139,20 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16054,7 +16167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16241,6 +16354,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
